--- a/发票模板导入格式示例.xlsx
+++ b/发票模板导入格式示例.xlsx
@@ -292,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,16 +311,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -332,15 +342,28 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -351,37 +374,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -393,7 +432,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -405,6 +446,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1377,222 +1419,222 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>US ELOGISTICS SERVICE CORP</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>Invoice #</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>发票号码.EL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">     Bill  To</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Terms</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>到期日</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>行项目.单价</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Please remit payment in full within 14 days. Thank you for your business!</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="33" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Beneficiary Name: (required)：Us Elogistics Service Corp</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>开票主体</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Beneficiary Account Number: (required)：8003139485</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>收款信息</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Bank Routing Number: (domestic wires)：3 | 2 | 2 | 0 | 7 | 0 | 3 | 8 | 1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>International：B|K| | |U|S| |3| |C| | |N| |A| |</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Name of Bank: Citibank New York</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Bank SWIFT Address: CITIUS33</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Account: 8003139485</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n"/>
-      <c r="C22" s="37" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="39" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1627,177 +1669,177 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>US ELOGISTICS SERVICE CORP</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>credit note #</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>发票号码.EL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">     Bill  To</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>行项目.单价.NEG</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Beneficiary Name: (required)：Us Elogistics Service Corp</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>开票主体</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Beneficiary Account Number: (required)：8003139485</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>收款信息</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>Bank Routing Number: (domestic wires)：3 | 2 | 2 | 0 | 7 | 0 | 3 | 8 | 1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>International：B|K| | |U|S| |3| |C| | |N| |A| |</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>Name of Bank: Citibank New York</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>Bank SWIFT Address: CITIUS33</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>Account: 8003139485</t>
         </is>
@@ -1833,221 +1875,221 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>ELOGISTICS (GA) SERVICE CORP</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>Invoice #</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>发票号码.GA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">     Bill  To</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>Terms</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>到期日</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="31" t="inlineStr">
         <is>
           <t>行项目.单价</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>Please remit payment in full within 14 days. Thank you for your business!</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E14" s="30" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="33" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Beneficiary Name: (required)：ELogistics (GA) Service Corp.</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>开票主体</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>Beneficiary Account Number: (required)：8003135707</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>收款信息</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>Bank Routing Number: (domestic wires)：0 | 6 | 1 | 1 | 0 | 3 | 8 | 8 | 4</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>International：B|K| | |U|S| |3| |C| | | |N| |A| |</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>Name of Bank: Citibank New York</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>Bank SWIFT Address: CITIUS33</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Account: 8003135707</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n"/>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="39" t="n"/>
+      <c r="B22" s="42" t="n"/>
+      <c r="D22" s="43" t="n"/>
+      <c r="E22" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2082,177 +2124,177 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>ELOGISTICS (GA) SERVICE CORP</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>credit note #</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>发票号码.GA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">     Bill  To</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
       </c>
-      <c r="D10" s="41" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr">
         <is>
           <t>行项目.单价.NEG</t>
         </is>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="45" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>Beneficiary Name: (required)：ELogistics (GA) Service Corp.</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>开票主体</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="47" t="inlineStr">
         <is>
           <t>Beneficiary Account Number: (required)：8003135707</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>收款信息</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>Bank Routing Number: (domestic wires)：0 | 6 | 1 | 1 | 0 | 3 | 8 | 8 | 4</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="47" t="inlineStr">
         <is>
           <t>International：B|K| | |U|S| |3| |C| | | |N| |A| |</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>Name of Bank: Citibank New York</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>Bank SWIFT Address: CITIUS33</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>Account: 8003135707</t>
         </is>
@@ -2290,64 +2332,64 @@
   <sheetData>
     <row r="1"/>
     <row r="4">
-      <c r="E4" s="43" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>発行日</t>
         </is>
       </c>
-      <c r="F4" s="44" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>开票日期.JP</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="50" t="inlineStr">
         <is>
           <t>発行番号</t>
         </is>
       </c>
-      <c r="F5" s="46" t="inlineStr">
+      <c r="F5" s="51" t="inlineStr">
         <is>
           <t>发票号码.JP</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="E6" s="43" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>登録番号</t>
         </is>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="48" t="inlineStr">
         <is>
           <t>T3010001214611</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>日発  株式会社</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>〒101-0051</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>住所：東京都墨田区横川一丁目9番3号</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="52" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
@@ -2355,31 +2397,31 @@
     </row>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>下記の通り、ご請求申し上げます。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>お振込み期日：</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>开票日期.JP</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
+      <c r="A17" s="53" t="inlineStr">
         <is>
           <t>ご請求金額 ：</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="54" t="inlineStr">
         <is>
           <t>合计金额(含税)</t>
         </is>
@@ -2418,234 +2460,234 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="55" t="inlineStr">
         <is>
           <t>行项目.序号</t>
         </is>
       </c>
-      <c r="B20" s="49" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>行项目.品名</t>
         </is>
       </c>
-      <c r="C20" s="49" t="inlineStr">
+      <c r="C20" s="55" t="inlineStr">
         <is>
           <t>行项目.账期.JP</t>
         </is>
       </c>
-      <c r="D20" s="49" t="inlineStr">
+      <c r="D20" s="55" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
       </c>
-      <c r="E20" s="49" t="inlineStr">
+      <c r="E20" s="55" t="inlineStr">
         <is>
           <t>行项目.单价</t>
         </is>
       </c>
-      <c r="F20" s="49" t="inlineStr">
+      <c r="F20" s="55" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="n"/>
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="50" t="n"/>
-      <c r="D21" s="50" t="n"/>
-      <c r="E21" s="50" t="n"/>
-      <c r="F21" s="50" t="n"/>
+      <c r="A21" s="56" t="n"/>
+      <c r="B21" s="56" t="n"/>
+      <c r="C21" s="56" t="n"/>
+      <c r="D21" s="56" t="n"/>
+      <c r="E21" s="56" t="n"/>
+      <c r="F21" s="56" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="n"/>
-      <c r="B22" s="50" t="n"/>
-      <c r="C22" s="50" t="n"/>
-      <c r="D22" s="50" t="n"/>
-      <c r="E22" s="50" t="n"/>
-      <c r="F22" s="50" t="n"/>
+      <c r="A22" s="56" t="n"/>
+      <c r="B22" s="56" t="n"/>
+      <c r="C22" s="56" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="56" t="n"/>
+      <c r="F22" s="56" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="n"/>
-      <c r="B23" s="50" t="n"/>
-      <c r="C23" s="50" t="n"/>
-      <c r="D23" s="50" t="n"/>
-      <c r="E23" s="50" t="n"/>
-      <c r="F23" s="50" t="n"/>
+      <c r="A23" s="56" t="n"/>
+      <c r="B23" s="56" t="n"/>
+      <c r="C23" s="56" t="n"/>
+      <c r="D23" s="56" t="n"/>
+      <c r="E23" s="56" t="n"/>
+      <c r="F23" s="56" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="n"/>
-      <c r="B24" s="50" t="n"/>
-      <c r="C24" s="50" t="n"/>
-      <c r="D24" s="50" t="n"/>
-      <c r="E24" s="50" t="n"/>
-      <c r="F24" s="50" t="n"/>
+      <c r="A24" s="56" t="n"/>
+      <c r="B24" s="56" t="n"/>
+      <c r="C24" s="56" t="n"/>
+      <c r="D24" s="56" t="n"/>
+      <c r="E24" s="56" t="n"/>
+      <c r="F24" s="56" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="n"/>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="50" t="n"/>
-      <c r="D25" s="50" t="n"/>
-      <c r="E25" s="50" t="n"/>
-      <c r="F25" s="50" t="n"/>
+      <c r="A25" s="56" t="n"/>
+      <c r="B25" s="56" t="n"/>
+      <c r="C25" s="56" t="n"/>
+      <c r="D25" s="56" t="n"/>
+      <c r="E25" s="56" t="n"/>
+      <c r="F25" s="56" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="n"/>
-      <c r="B26" s="50" t="n"/>
-      <c r="C26" s="50" t="n"/>
-      <c r="D26" s="50" t="n"/>
-      <c r="E26" s="50" t="n"/>
-      <c r="F26" s="50" t="n"/>
+      <c r="A26" s="56" t="n"/>
+      <c r="B26" s="56" t="n"/>
+      <c r="C26" s="56" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="56" t="n"/>
+      <c r="F26" s="56" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="n"/>
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="50" t="n"/>
-      <c r="D27" s="50" t="n"/>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="50" t="n"/>
+      <c r="A27" s="56" t="n"/>
+      <c r="B27" s="56" t="n"/>
+      <c r="C27" s="56" t="n"/>
+      <c r="D27" s="56" t="n"/>
+      <c r="E27" s="56" t="n"/>
+      <c r="F27" s="56" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="n"/>
-      <c r="B28" s="50" t="n"/>
-      <c r="C28" s="50" t="n"/>
-      <c r="D28" s="50" t="n"/>
-      <c r="E28" s="50" t="n"/>
-      <c r="F28" s="50" t="n"/>
+      <c r="A28" s="56" t="n"/>
+      <c r="B28" s="56" t="n"/>
+      <c r="C28" s="56" t="n"/>
+      <c r="D28" s="56" t="n"/>
+      <c r="E28" s="56" t="n"/>
+      <c r="F28" s="56" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="n"/>
-      <c r="B29" s="50" t="n"/>
-      <c r="C29" s="50" t="n"/>
-      <c r="D29" s="50" t="n"/>
-      <c r="E29" s="50" t="n"/>
-      <c r="F29" s="50" t="n"/>
+      <c r="A29" s="56" t="n"/>
+      <c r="B29" s="56" t="n"/>
+      <c r="C29" s="56" t="n"/>
+      <c r="D29" s="56" t="n"/>
+      <c r="E29" s="56" t="n"/>
+      <c r="F29" s="56" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="50" t="n"/>
-      <c r="B30" s="50" t="n"/>
-      <c r="C30" s="50" t="n"/>
-      <c r="D30" s="50" t="n"/>
-      <c r="E30" s="50" t="n"/>
-      <c r="F30" s="50" t="n"/>
+      <c r="A30" s="56" t="n"/>
+      <c r="B30" s="56" t="n"/>
+      <c r="C30" s="56" t="n"/>
+      <c r="D30" s="56" t="n"/>
+      <c r="E30" s="56" t="n"/>
+      <c r="F30" s="56" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="n"/>
-      <c r="B31" s="50" t="n"/>
-      <c r="C31" s="50" t="n"/>
-      <c r="D31" s="50" t="n"/>
-      <c r="E31" s="50" t="n"/>
-      <c r="F31" s="50" t="n"/>
+      <c r="A31" s="56" t="n"/>
+      <c r="B31" s="56" t="n"/>
+      <c r="C31" s="56" t="n"/>
+      <c r="D31" s="56" t="n"/>
+      <c r="E31" s="56" t="n"/>
+      <c r="F31" s="56" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="n"/>
-      <c r="B32" s="50" t="n"/>
-      <c r="C32" s="50" t="n"/>
-      <c r="D32" s="50" t="n"/>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="50" t="n"/>
+      <c r="A32" s="56" t="n"/>
+      <c r="B32" s="56" t="n"/>
+      <c r="C32" s="56" t="n"/>
+      <c r="D32" s="56" t="n"/>
+      <c r="E32" s="56" t="n"/>
+      <c r="F32" s="56" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="n"/>
-      <c r="B33" s="50" t="n"/>
-      <c r="C33" s="50" t="n"/>
-      <c r="D33" s="50" t="n"/>
-      <c r="E33" s="50" t="n"/>
-      <c r="F33" s="50" t="n"/>
+      <c r="A33" s="56" t="n"/>
+      <c r="B33" s="56" t="n"/>
+      <c r="C33" s="56" t="n"/>
+      <c r="D33" s="56" t="n"/>
+      <c r="E33" s="56" t="n"/>
+      <c r="F33" s="56" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="n"/>
-      <c r="B34" s="50" t="n"/>
-      <c r="C34" s="50" t="n"/>
-      <c r="D34" s="50" t="n"/>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="50" t="n"/>
+      <c r="A34" s="56" t="n"/>
+      <c r="B34" s="56" t="n"/>
+      <c r="C34" s="56" t="n"/>
+      <c r="D34" s="56" t="n"/>
+      <c r="E34" s="56" t="n"/>
+      <c r="F34" s="56" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="n"/>
-      <c r="B35" s="50" t="n"/>
-      <c r="C35" s="50" t="n"/>
-      <c r="D35" s="50" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="50" t="n"/>
+      <c r="A35" s="56" t="n"/>
+      <c r="B35" s="56" t="n"/>
+      <c r="C35" s="56" t="n"/>
+      <c r="D35" s="56" t="n"/>
+      <c r="E35" s="56" t="n"/>
+      <c r="F35" s="56" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="57" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="B36" s="50" t="n"/>
-      <c r="C36" s="50" t="n"/>
-      <c r="D36" s="50" t="n"/>
+      <c r="B36" s="56" t="n"/>
+      <c r="C36" s="56" t="n"/>
+      <c r="D36" s="56" t="n"/>
       <c r="E36" s="5" t="inlineStr">
         <is>
           <t>小計</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>小计金额.JP</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="50" t="n"/>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="50" t="n"/>
-      <c r="D37" s="50" t="n"/>
+      <c r="A37" s="56" t="n"/>
+      <c r="B37" s="56" t="n"/>
+      <c r="C37" s="56" t="n"/>
+      <c r="D37" s="56" t="n"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>消費税</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>消费税额.JP</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="n"/>
-      <c r="B38" s="50" t="n"/>
-      <c r="C38" s="50" t="n"/>
-      <c r="D38" s="50" t="n"/>
+      <c r="A38" s="56" t="n"/>
+      <c r="B38" s="56" t="n"/>
+      <c r="C38" s="56" t="n"/>
+      <c r="D38" s="56" t="n"/>
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>合計（税込み）</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>合计金额(含税)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>お振込先</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="51" t="inlineStr">
+      <c r="A41" s="58" t="inlineStr">
         <is>
           <t>[振込先] シティバンク、エヌ・エイ 東京支店</t>
         </is>
       </c>
-      <c r="B41" s="52" t="n"/>
+      <c r="B41" s="59" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="53" t="inlineStr">
+      <c r="A42" s="60" t="inlineStr">
         <is>
           <t>当座預金 9904695 NICHIHATU KABUSIKIGAISYA</t>
         </is>
       </c>
-      <c r="B42" s="54" t="n"/>
+      <c r="B42" s="61" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>*恐れ入りますが、お振込み手数料はご負担願います。</t>
         </is>
@@ -2681,310 +2723,310 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>TAX INVOICE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Invoice Date</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>开票日期.AU</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Everfast Pty Ltd</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>开票日期.AU</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>42-62 POUND ROAD W, DANDENONG SOUTH VIC 3175</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>发票号码.AU</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>ABN</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>75 623 285 825</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="63" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C13" s="56" t="inlineStr">
+      <c r="C13" s="63" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D13" s="56" t="inlineStr">
+      <c r="D13" s="63" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="E13" s="56" t="inlineStr">
+      <c r="E13" s="63" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="F13" s="56" t="inlineStr">
+      <c r="F13" s="63" t="inlineStr">
         <is>
           <t>Amount AUD</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="48" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>行项目.描述.AU</t>
         </is>
       </c>
-      <c r="C14" s="48" t="inlineStr">
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
       </c>
-      <c r="D14" s="48" t="inlineStr">
+      <c r="D14" s="54" t="inlineStr">
         <is>
           <t>行项目.单价</t>
         </is>
       </c>
-      <c r="E14" s="48" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>GST(10%).AU</t>
         </is>
       </c>
-      <c r="F14" s="48" t="inlineStr">
+      <c r="F14" s="54" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="37" t="n"/>
-      <c r="C15" s="37" t="n"/>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="37" t="n"/>
-      <c r="F15" s="37" t="n"/>
+      <c r="B15" s="42" t="n"/>
+      <c r="C15" s="42" t="n"/>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
+      <c r="F15" s="42" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="37" t="n"/>
-      <c r="C16" s="37" t="n"/>
-      <c r="D16" s="37" t="n"/>
-      <c r="E16" s="37" t="n"/>
-      <c r="F16" s="37" t="n"/>
+      <c r="B16" s="42" t="n"/>
+      <c r="C16" s="42" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
+      <c r="F16" s="42" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="37" t="n"/>
-      <c r="C17" s="37" t="n"/>
-      <c r="D17" s="37" t="n"/>
-      <c r="E17" s="37" t="n"/>
-      <c r="F17" s="37" t="n"/>
+      <c r="B17" s="42" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
+      <c r="F17" s="42" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="37" t="n"/>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="37" t="n"/>
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="42" t="n"/>
+      <c r="D18" s="42" t="n"/>
+      <c r="E18" s="42" t="n"/>
+      <c r="F18" s="42" t="n"/>
     </row>
     <row r="20">
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>小计金额.AU</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>TOTAL GST 10%</t>
         </is>
       </c>
-      <c r="F21" s="57" t="inlineStr">
+      <c r="F21" s="64" t="inlineStr">
         <is>
           <t>合计税额.AU</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>TOTAL AUD</t>
         </is>
       </c>
-      <c r="F22" s="57" t="inlineStr">
+      <c r="F22" s="64" t="inlineStr">
         <is>
           <t>合计金额(含税)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Due Date:</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>到期日</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Bank Name: Citibank</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Account Name: Everfast Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>BSB: 242-000</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Account No: 236077004</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="65" t="inlineStr">
         <is>
           <t>PAYMENT ADVICE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>To:</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>发票号码.AU</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>Amount Due</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>合计金额(含税)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>42-62 POUND ROAD W,
 DANDENONG SOUTH VIC 3175</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>到期日</t>
         </is>
@@ -3024,10 +3066,10 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="66" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>深圳市云颂国际货运代理有限公司
 ShenZhen YunSong International Freight Forwarding Co. LTD
@@ -3038,235 +3080,235 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>To：</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>开票日期.ABU</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>Address:</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>Invoice No.</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>发票号码.SZ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>商品/服务描述 Description</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>期间 Period</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>金额（USD） Amount(USD)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="E8" s="63" t="n"/>
+      <c r="E8" s="72" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
-      <c r="E9" s="63" t="n"/>
+      <c r="E9" s="72" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="64" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>行项目.品名</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>行项目.账期.ABU</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
+      <c r="E10" s="74" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="66" t="n"/>
-      <c r="E11" s="63" t="n"/>
+      <c r="B11" s="75" t="n"/>
+      <c r="E11" s="72" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="66" t="n"/>
-      <c r="E12" s="63" t="n"/>
+      <c r="B12" s="75" t="n"/>
+      <c r="E12" s="72" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="66" t="n"/>
-      <c r="E13" s="63" t="n"/>
+      <c r="B13" s="75" t="n"/>
+      <c r="E13" s="72" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="66" t="n"/>
-      <c r="E14" s="63" t="n"/>
+      <c r="B14" s="75" t="n"/>
+      <c r="E14" s="72" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="66" t="n"/>
-      <c r="E15" s="63" t="n"/>
+      <c r="B15" s="75" t="n"/>
+      <c r="E15" s="72" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="66" t="n"/>
-      <c r="E16" s="63" t="n"/>
+      <c r="B16" s="75" t="n"/>
+      <c r="E16" s="72" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>合计（USD）：Total（USD）</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>请支付到以下账户（Please Pay To The Following Account）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="69" t="inlineStr">
+      <c r="B19" s="78" t="inlineStr">
         <is>
           <t>收款人名称：(Name Of Beneficiary)</t>
         </is>
       </c>
-      <c r="C19" s="70" t="inlineStr">
+      <c r="C19" s="79" t="inlineStr">
         <is>
           <t>收款人名称</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="69" t="inlineStr">
+      <c r="B20" s="78" t="inlineStr">
         <is>
           <t>银行名称 (Bank Name)</t>
         </is>
       </c>
-      <c r="C20" s="70" t="inlineStr">
+      <c r="C20" s="79" t="inlineStr">
         <is>
           <t>银行名称</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="69" t="inlineStr">
+      <c r="B21" s="78" t="inlineStr">
         <is>
           <t>账户名称 Account Name</t>
         </is>
       </c>
-      <c r="C21" s="70" t="inlineStr">
+      <c r="C21" s="79" t="inlineStr">
         <is>
           <t>账户名称</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="69" t="inlineStr">
+      <c r="B22" s="78" t="inlineStr">
         <is>
           <t>账户号 (Account Number)</t>
         </is>
       </c>
-      <c r="C22" s="70" t="inlineStr">
+      <c r="C22" s="79" t="inlineStr">
         <is>
           <t>账号</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="69" t="inlineStr">
+      <c r="B23" s="78" t="inlineStr">
         <is>
           <t>银行代码 (Bank code)</t>
         </is>
       </c>
-      <c r="C23" s="70" t="inlineStr">
+      <c r="C23" s="79" t="inlineStr">
         <is>
           <t>银行代码</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="69" t="inlineStr">
+      <c r="B24" s="78" t="inlineStr">
         <is>
           <t>银行联行码 (Bank Swift Code)</t>
         </is>
       </c>
-      <c r="C24" s="70" t="inlineStr">
+      <c r="C24" s="79" t="inlineStr">
         <is>
           <t>Swift Code</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="69" t="inlineStr">
+      <c r="B25" s="78" t="inlineStr">
         <is>
           <t>银行地址 (Bank Address)</t>
         </is>
       </c>
-      <c r="C25" s="70" t="inlineStr">
+      <c r="C25" s="79" t="inlineStr">
         <is>
           <t>银行地址</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="71" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>发票备注：(Comment)</t>
         </is>
       </c>
-      <c r="C26" s="70" t="inlineStr">
+      <c r="C26" s="79" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="E26" s="39" t="n"/>
+      <c r="E26" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3317,10 +3359,10 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="11" t="inlineStr"/>
+      <c r="B2" s="66" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="66" t="inlineStr">
         <is>
           <t>香港雲頌國際貨運有限公司
 HONGKONG YUNFREIGHT LIMITED
@@ -3331,235 +3373,235 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="58" t="inlineStr">
+      <c r="B5" s="67" t="inlineStr">
         <is>
           <t>To：</t>
         </is>
       </c>
-      <c r="D5" s="59" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>开票日期.ABU</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="58" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>Address:</t>
         </is>
       </c>
-      <c r="D6" s="59" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
         <is>
           <t>Invoice No.</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>发票号码.HK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>商品/服务描述 Description</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>期间 Period</t>
         </is>
       </c>
-      <c r="E7" s="61" t="inlineStr">
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>金额（USD） Amount(USD)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="62" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
-      <c r="E8" s="63" t="n"/>
+      <c r="E8" s="72" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="62" t="inlineStr">
+      <c r="B9" s="71" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
-      <c r="E9" s="63" t="n"/>
+      <c r="E9" s="72" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="64" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>行项目.品名</t>
         </is>
       </c>
-      <c r="C10" s="41" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>行项目.账期.ABU</t>
         </is>
       </c>
-      <c r="E10" s="65" t="inlineStr">
+      <c r="E10" s="74" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="66" t="n"/>
-      <c r="E11" s="63" t="n"/>
+      <c r="B11" s="75" t="n"/>
+      <c r="E11" s="72" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="66" t="n"/>
-      <c r="E12" s="63" t="n"/>
+      <c r="B12" s="75" t="n"/>
+      <c r="E12" s="72" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="66" t="n"/>
-      <c r="E13" s="63" t="n"/>
+      <c r="B13" s="75" t="n"/>
+      <c r="E13" s="72" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="66" t="n"/>
-      <c r="E14" s="63" t="n"/>
+      <c r="B14" s="75" t="n"/>
+      <c r="E14" s="72" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="66" t="n"/>
-      <c r="E15" s="63" t="n"/>
+      <c r="B15" s="75" t="n"/>
+      <c r="E15" s="72" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="66" t="n"/>
-      <c r="E16" s="63" t="n"/>
+      <c r="B16" s="75" t="n"/>
+      <c r="E16" s="72" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="67" t="inlineStr">
+      <c r="B17" s="76" t="inlineStr">
         <is>
           <t>合计（USD）：Total（USD）</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B18" s="77" t="inlineStr">
         <is>
           <t>请支付到以下账户（Please Pay To The Following Account）</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="69" t="inlineStr">
+      <c r="B19" s="78" t="inlineStr">
         <is>
           <t>收款人名称：(Name Of Beneficiary)</t>
         </is>
       </c>
-      <c r="C19" s="70" t="inlineStr">
+      <c r="C19" s="79" t="inlineStr">
         <is>
           <t>收款人名称</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="69" t="inlineStr">
+      <c r="B20" s="78" t="inlineStr">
         <is>
           <t>银行名称 (Bank Name)</t>
         </is>
       </c>
-      <c r="C20" s="70" t="inlineStr">
+      <c r="C20" s="79" t="inlineStr">
         <is>
           <t>银行名称</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="69" t="inlineStr">
+      <c r="B21" s="78" t="inlineStr">
         <is>
           <t>账户名称 Account Name</t>
         </is>
       </c>
-      <c r="C21" s="70" t="inlineStr">
+      <c r="C21" s="79" t="inlineStr">
         <is>
           <t>账户名称</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="69" t="inlineStr">
+      <c r="B22" s="78" t="inlineStr">
         <is>
           <t>账户号 (Account Number)</t>
         </is>
       </c>
-      <c r="C22" s="70" t="inlineStr">
+      <c r="C22" s="79" t="inlineStr">
         <is>
           <t>账号</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="69" t="inlineStr">
+      <c r="B23" s="78" t="inlineStr">
         <is>
           <t>银行代码 (Bank code)</t>
         </is>
       </c>
-      <c r="C23" s="70" t="inlineStr">
+      <c r="C23" s="79" t="inlineStr">
         <is>
           <t>银行代码</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="69" t="inlineStr">
+      <c r="B24" s="78" t="inlineStr">
         <is>
           <t>银行联行码 (Bank Swift Code)</t>
         </is>
       </c>
-      <c r="C24" s="70" t="inlineStr">
+      <c r="C24" s="79" t="inlineStr">
         <is>
           <t>Swift Code</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="69" t="inlineStr">
+      <c r="B25" s="78" t="inlineStr">
         <is>
           <t>银行地址 (Bank Address)</t>
         </is>
       </c>
-      <c r="C25" s="70" t="inlineStr">
+      <c r="C25" s="79" t="inlineStr">
         <is>
           <t>银行地址</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="71" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>发票备注：(Comment)</t>
         </is>
       </c>
-      <c r="C26" s="70" t="inlineStr">
+      <c r="C26" s="79" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
-      <c r="E26" s="39" t="n"/>
+      <c r="E26" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -3611,40 +3653,40 @@
   </cols>
   <sheetData>
     <row r="4">
-      <c r="C4" s="72" t="inlineStr">
+      <c r="C4" s="81" t="inlineStr">
         <is>
           <t>字段key（红字内容）</t>
         </is>
       </c>
-      <c r="D4" s="72" t="inlineStr">
+      <c r="D4" s="81" t="inlineStr">
         <is>
           <t>取值类型</t>
         </is>
       </c>
-      <c r="E4" s="72" t="inlineStr">
+      <c r="E4" s="81" t="inlineStr">
         <is>
           <t>取值逻辑</t>
         </is>
       </c>
-      <c r="F4" s="72" t="inlineStr">
+      <c r="F4" s="81" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="73" t="inlineStr">
+      <c r="B5" s="82" t="inlineStr">
         <is>
           <t>申请单映射字段</t>
         </is>
       </c>
-      <c r="C5" s="74" t="n"/>
-      <c r="D5" s="74" t="n"/>
-      <c r="E5" s="74" t="n"/>
-      <c r="F5" s="74" t="n"/>
+      <c r="C5" s="83" t="n"/>
+      <c r="D5" s="83" t="n"/>
+      <c r="E5" s="83" t="n"/>
+      <c r="F5" s="83" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
@@ -3654,19 +3696,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E6" s="75" t="inlineStr">
+      <c r="E6" s="84" t="inlineStr">
         <is>
           <t>申请单-&gt;客户名称</t>
         </is>
       </c>
-      <c r="F6" s="75" t="inlineStr">
+      <c r="F6" s="84" t="inlineStr">
         <is>
           <t>所有模板通用</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
@@ -3676,15 +3718,15 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E7" s="75" t="inlineStr">
+      <c r="E7" s="84" t="inlineStr">
         <is>
           <t>申请单-&gt;客户地址</t>
         </is>
       </c>
-      <c r="F7" s="75" t="inlineStr"/>
+      <c r="F7" s="84" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
@@ -3694,19 +3736,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E8" s="75" t="inlineStr">
+      <c r="E8" s="84" t="inlineStr">
         <is>
           <t>ITS-&gt;账期最后一天/审核当天</t>
         </is>
       </c>
-      <c r="F8" s="75" t="inlineStr">
+      <c r="F8" s="84" t="inlineStr">
         <is>
           <t>格式:mm/dd/yyyy - EL/GA/CA</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>开票日期.VC</t>
         </is>
@@ -3716,19 +3758,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E9" s="75" t="inlineStr">
+      <c r="E9" s="84" t="inlineStr">
         <is>
           <t>ITS-&gt;账期最后一天/审核当天</t>
         </is>
       </c>
-      <c r="F9" s="75" t="inlineStr">
+      <c r="F9" s="84" t="inlineStr">
         <is>
           <t>格式:Mon/dd/yyyy - 温哥华</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>开票日期.JP</t>
         </is>
@@ -3738,19 +3780,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E10" s="75" t="inlineStr">
+      <c r="E10" s="84" t="inlineStr">
         <is>
           <t>ITS-&gt;账期最后一天/审核当天</t>
         </is>
       </c>
-      <c r="F10" s="75" t="inlineStr">
+      <c r="F10" s="84" t="inlineStr">
         <is>
           <t>格式:yyyy年mm月dd日</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>开票日期.AU</t>
         </is>
@@ -3760,19 +3802,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E11" s="75" t="inlineStr">
+      <c r="E11" s="84" t="inlineStr">
         <is>
           <t>ITS-&gt;账期最后一天/审核当天</t>
         </is>
       </c>
-      <c r="F11" s="75" t="inlineStr">
+      <c r="F11" s="84" t="inlineStr">
         <is>
           <t>格式:dd-mm-yyyy</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>开票日期.ABU</t>
         </is>
@@ -3782,19 +3824,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E12" s="75" t="inlineStr">
+      <c r="E12" s="84" t="inlineStr">
         <is>
           <t>审核当天</t>
         </is>
       </c>
-      <c r="F12" s="75" t="inlineStr">
+      <c r="F12" s="84" t="inlineStr">
         <is>
           <t>格式:yyyy-mm-dd - ABU</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.EL</t>
         </is>
@@ -3804,19 +3846,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E13" s="75" t="inlineStr">
+      <c r="E13" s="84" t="inlineStr">
         <is>
           <t>公司简称+US+yyyymmdd+B+4seq</t>
         </is>
       </c>
-      <c r="F13" s="75" t="inlineStr">
+      <c r="F13" s="84" t="inlineStr">
         <is>
           <t>美国EL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>发票号码.GA</t>
         </is>
@@ -3826,19 +3868,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E14" s="75" t="inlineStr">
+      <c r="E14" s="84" t="inlineStr">
         <is>
           <t>公司简称+US+yyyymmdd+B+4seq</t>
         </is>
       </c>
-      <c r="F14" s="75" t="inlineStr">
+      <c r="F14" s="84" t="inlineStr">
         <is>
           <t>美国GA</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>发票号码.JP</t>
         </is>
@@ -3848,19 +3890,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E15" s="75" t="inlineStr">
+      <c r="E15" s="84" t="inlineStr">
         <is>
           <t>NF+yyyy-mmdd+2seq</t>
         </is>
       </c>
-      <c r="F15" s="75" t="inlineStr">
+      <c r="F15" s="84" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>发票号码.AU</t>
         </is>
@@ -3870,19 +3912,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E16" s="84" t="inlineStr">
         <is>
           <t>EPAUS+yyyymm+B+3seq</t>
         </is>
       </c>
-      <c r="F16" s="75" t="inlineStr">
+      <c r="F16" s="84" t="inlineStr">
         <is>
           <t>澳洲</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>发票号码.CA</t>
         </is>
@@ -3892,19 +3934,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E17" s="75" t="inlineStr">
+      <c r="E17" s="84" t="inlineStr">
         <is>
           <t>GCCA+yyyymm+B+4seq</t>
         </is>
       </c>
-      <c r="F17" s="75" t="inlineStr">
+      <c r="F17" s="84" t="inlineStr">
         <is>
           <t>加拿大</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>发票号码.VC</t>
         </is>
@@ -3914,19 +3956,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E18" s="75" t="inlineStr">
+      <c r="E18" s="84" t="inlineStr">
         <is>
           <t>YTTY+yyyymm+B+4seq</t>
         </is>
       </c>
-      <c r="F18" s="75" t="inlineStr">
+      <c r="F18" s="84" t="inlineStr">
         <is>
           <t>温哥华</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>发票号码.SZ</t>
         </is>
@@ -3936,19 +3978,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E19" s="75" t="inlineStr">
+      <c r="E19" s="84" t="inlineStr">
         <is>
           <t>YSSZ+yyyymm+F+4seq</t>
         </is>
       </c>
-      <c r="F19" s="75" t="inlineStr">
+      <c r="F19" s="84" t="inlineStr">
         <is>
           <t>深圳</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>发票号码.HK</t>
         </is>
@@ -3958,19 +4000,19 @@
           <t>规则计算</t>
         </is>
       </c>
-      <c r="E20" s="75" t="inlineStr">
+      <c r="E20" s="84" t="inlineStr">
         <is>
           <t>YSHK+yyyymm+F+4seq</t>
         </is>
       </c>
-      <c r="F20" s="75" t="inlineStr">
+      <c r="F20" s="84" t="inlineStr">
         <is>
           <t>香港</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
@@ -3980,19 +4022,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E21" s="75" t="inlineStr">
+      <c r="E21" s="84" t="inlineStr">
         <is>
           <t>申请单-&gt;付款条款</t>
         </is>
       </c>
-      <c r="F21" s="75" t="inlineStr">
+      <c r="F21" s="84" t="inlineStr">
         <is>
           <t>如Net 14, Net 30</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>到期日</t>
         </is>
@@ -4002,30 +4044,30 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E22" s="75" t="inlineStr">
+      <c r="E22" s="84" t="inlineStr">
         <is>
           <t>开票日期+付款周期天数</t>
         </is>
       </c>
-      <c r="F22" s="75" t="inlineStr">
+      <c r="F22" s="84" t="inlineStr">
         <is>
           <t>EL/GA/加拿大/温哥华</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="73" t="inlineStr">
+      <c r="B23" s="82" t="inlineStr">
         <is>
           <t>系统生成/计算字段</t>
         </is>
       </c>
-      <c r="C23" s="74" t="n"/>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="74" t="n"/>
-      <c r="F23" s="74" t="n"/>
+      <c r="C23" s="83" t="n"/>
+      <c r="D23" s="83" t="n"/>
+      <c r="E23" s="83" t="n"/>
+      <c r="F23" s="83" t="n"/>
     </row>
     <row r="24">
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>币种</t>
         </is>
@@ -4035,15 +4077,15 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E24" s="75" t="inlineStr">
+      <c r="E24" s="84" t="inlineStr">
         <is>
           <t>申请单-&gt;币种</t>
         </is>
       </c>
-      <c r="F24" s="75" t="inlineStr"/>
+      <c r="F24" s="84" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
@@ -4053,19 +4095,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E25" s="75" t="inlineStr">
+      <c r="E25" s="84" t="inlineStr">
         <is>
           <t>申请单-&gt;发票备注</t>
         </is>
       </c>
-      <c r="F25" s="75" t="inlineStr">
+      <c r="F25" s="84" t="inlineStr">
         <is>
           <t>无值则留空</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
@@ -4075,19 +4117,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E26" s="75" t="inlineStr">
+      <c r="E26" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.金额)</t>
         </is>
       </c>
-      <c r="F26" s="75" t="inlineStr">
+      <c r="F26" s="84" t="inlineStr">
         <is>
           <t>不含税合计</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
@@ -4097,19 +4139,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E27" s="75" t="inlineStr">
+      <c r="E27" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.金额.NEG)</t>
         </is>
       </c>
-      <c r="F27" s="75" t="inlineStr">
+      <c r="F27" s="84" t="inlineStr">
         <is>
           <t>负数模版</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>合计税额</t>
         </is>
@@ -4119,19 +4161,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E28" s="75" t="inlineStr">
+      <c r="E28" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.税额)</t>
         </is>
       </c>
-      <c r="F28" s="75" t="inlineStr">
+      <c r="F28" s="84" t="inlineStr">
         <is>
           <t>CA/VC</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>合计税额.NEG</t>
         </is>
@@ -4141,19 +4183,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E29" s="75" t="inlineStr">
+      <c r="E29" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.税额.NEG)</t>
         </is>
       </c>
-      <c r="F29" s="75" t="inlineStr">
+      <c r="F29" s="84" t="inlineStr">
         <is>
           <t>负数模版</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="15" t="inlineStr">
         <is>
           <t>合计含税金额</t>
         </is>
@@ -4163,19 +4205,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E30" s="75" t="inlineStr">
+      <c r="E30" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.含税金额)</t>
         </is>
       </c>
-      <c r="F30" s="75" t="inlineStr">
+      <c r="F30" s="84" t="inlineStr">
         <is>
           <t>CA/VC</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>合计含税金额.NEG</t>
         </is>
@@ -4185,19 +4227,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E31" s="75" t="inlineStr">
+      <c r="E31" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.含税金额.NEG)</t>
         </is>
       </c>
-      <c r="F31" s="75" t="inlineStr">
+      <c r="F31" s="84" t="inlineStr">
         <is>
           <t>负数模版</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>小计金额.JP</t>
         </is>
@@ -4207,19 +4249,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E32" s="75" t="inlineStr">
+      <c r="E32" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.金额)</t>
         </is>
       </c>
-      <c r="F32" s="75" t="inlineStr">
+      <c r="F32" s="84" t="inlineStr">
         <is>
           <t>日本谷仓使用</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>消费税额.JP</t>
         </is>
@@ -4229,19 +4271,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E33" s="75" t="inlineStr">
+      <c r="E33" s="84" t="inlineStr">
         <is>
           <t>小计金额*10%</t>
         </is>
       </c>
-      <c r="F33" s="75" t="inlineStr">
+      <c r="F33" s="84" t="inlineStr">
         <is>
           <t>日本谷仓消费税</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>小计金额.AU</t>
         </is>
@@ -4251,19 +4293,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E34" s="75" t="inlineStr">
+      <c r="E34" s="84" t="inlineStr">
         <is>
           <t>SUM(行项目.金额)</t>
         </is>
       </c>
-      <c r="F34" s="75" t="inlineStr">
+      <c r="F34" s="84" t="inlineStr">
         <is>
           <t>澳洲使用</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>合计税额.AU</t>
         </is>
@@ -4273,19 +4315,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E35" s="75" t="inlineStr">
+      <c r="E35" s="84" t="inlineStr">
         <is>
           <t>小计金额*10%</t>
         </is>
       </c>
-      <c r="F35" s="75" t="inlineStr">
+      <c r="F35" s="84" t="inlineStr">
         <is>
           <t>澳洲GST总额</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
         <is>
           <t>合计含税金额</t>
         </is>
@@ -4295,30 +4337,30 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E36" s="75" t="inlineStr">
+      <c r="E36" s="84" t="inlineStr">
         <is>
           <t>合计金额+合计税额</t>
         </is>
       </c>
-      <c r="F36" s="75" t="inlineStr">
+      <c r="F36" s="84" t="inlineStr">
         <is>
           <t>CA/VC/JP/AU</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="73" t="inlineStr">
+      <c r="B37" s="82" t="inlineStr">
         <is>
           <t>行项目区字段</t>
         </is>
       </c>
-      <c r="C37" s="74" t="n"/>
-      <c r="D37" s="74" t="n"/>
-      <c r="E37" s="74" t="n"/>
-      <c r="F37" s="74" t="n"/>
+      <c r="C37" s="83" t="n"/>
+      <c r="D37" s="83" t="n"/>
+      <c r="E37" s="83" t="n"/>
+      <c r="F37" s="83" t="n"/>
     </row>
     <row r="38">
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="15" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
@@ -4328,19 +4370,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E38" s="75" t="inlineStr">
+      <c r="E38" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;品名+' for '+账期(m/d/y-m/d/y)</t>
         </is>
       </c>
-      <c r="F38" s="75" t="inlineStr">
+      <c r="F38" s="84" t="inlineStr">
         <is>
           <t>EL/GA/CA/VC</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>行项目.描述.AU</t>
         </is>
@@ -4350,19 +4392,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E39" s="75" t="inlineStr">
+      <c r="E39" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;品名+'--'+账期(dd/mm/yyyy-dd/mm/yyyy)</t>
         </is>
       </c>
-      <c r="F39" s="75" t="inlineStr">
+      <c r="F39" s="84" t="inlineStr">
         <is>
           <t>澳洲</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>行项目.品名</t>
         </is>
@@ -4372,19 +4414,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E40" s="75" t="inlineStr">
+      <c r="E40" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;品名</t>
         </is>
       </c>
-      <c r="F40" s="75" t="inlineStr">
+      <c r="F40" s="84" t="inlineStr">
         <is>
           <t>日本/ABU</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>行项目.序号</t>
         </is>
@@ -4394,19 +4436,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E41" s="75" t="inlineStr">
+      <c r="E41" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;序号</t>
         </is>
       </c>
-      <c r="F41" s="75" t="inlineStr">
+      <c r="F41" s="84" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>行项目.账期.US</t>
         </is>
@@ -4416,19 +4458,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E42" s="75" t="inlineStr">
+      <c r="E42" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;账期</t>
         </is>
       </c>
-      <c r="F42" s="75" t="inlineStr">
+      <c r="F42" s="84" t="inlineStr">
         <is>
           <t>格式:mm/dd/yyyy-mm/dd/yyyy</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>行项目.账期.JP</t>
         </is>
@@ -4438,19 +4480,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E43" s="75" t="inlineStr">
+      <c r="E43" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;账期</t>
         </is>
       </c>
-      <c r="F43" s="75" t="inlineStr">
+      <c r="F43" s="84" t="inlineStr">
         <is>
           <t>格式:yyyy/mm/dd-yyyy/mm/dd</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="15" t="inlineStr">
         <is>
           <t>行项目.账期.AU</t>
         </is>
@@ -4460,19 +4502,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E44" s="75" t="inlineStr">
+      <c r="E44" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;账期</t>
         </is>
       </c>
-      <c r="F44" s="75" t="inlineStr">
+      <c r="F44" s="84" t="inlineStr">
         <is>
           <t>格式:dd/mm/yyyy-dd/mm/yyyy</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>行项目.账期.ABU</t>
         </is>
@@ -4482,19 +4524,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E45" s="75" t="inlineStr">
+      <c r="E45" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;账期</t>
         </is>
       </c>
-      <c r="F45" s="75" t="inlineStr">
+      <c r="F45" s="84" t="inlineStr">
         <is>
           <t>格式:yyyy-mm-dd至yyyy-mm-dd</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>行项目.数量</t>
         </is>
@@ -4504,19 +4546,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E46" s="75" t="inlineStr">
+      <c r="E46" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;数量</t>
         </is>
       </c>
-      <c r="F46" s="75" t="inlineStr">
+      <c r="F46" s="84" t="inlineStr">
         <is>
           <t>默认1</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>行项目.单价</t>
         </is>
@@ -4526,15 +4568,15 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E47" s="75" t="inlineStr">
+      <c r="E47" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;单价</t>
         </is>
       </c>
-      <c r="F47" s="75" t="inlineStr"/>
+      <c r="F47" s="84" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
@@ -4544,19 +4586,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E48" s="75" t="inlineStr">
+      <c r="E48" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;金额</t>
         </is>
       </c>
-      <c r="F48" s="75" t="inlineStr">
+      <c r="F48" s="84" t="inlineStr">
         <is>
           <t>不含税</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
@@ -4566,19 +4608,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E49" s="75" t="inlineStr">
+      <c r="E49" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;金额 * (-1)</t>
         </is>
       </c>
-      <c r="F49" s="75" t="inlineStr">
+      <c r="F49" s="84" t="inlineStr">
         <is>
           <t>负数模版取反</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>行项目.单价.NEG</t>
         </is>
@@ -4588,19 +4630,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E50" s="75" t="inlineStr">
+      <c r="E50" s="84" t="inlineStr">
         <is>
           <t>行项目-&gt;单价 * (-1)</t>
         </is>
       </c>
-      <c r="F50" s="75" t="inlineStr">
+      <c r="F50" s="84" t="inlineStr">
         <is>
           <t>负数模版取反</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>行项目.税额</t>
         </is>
@@ -4610,19 +4652,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E51" s="75" t="inlineStr">
+      <c r="E51" s="84" t="inlineStr">
         <is>
           <t>金额 * 税率</t>
         </is>
       </c>
-      <c r="F51" s="75" t="inlineStr">
+      <c r="F51" s="84" t="inlineStr">
         <is>
           <t>CA/VC</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>行项目.税额.NEG</t>
         </is>
@@ -4632,19 +4674,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E52" s="75" t="inlineStr">
+      <c r="E52" s="84" t="inlineStr">
         <is>
           <t>金额 * 税率 * (-1)</t>
         </is>
       </c>
-      <c r="F52" s="75" t="inlineStr">
+      <c r="F52" s="84" t="inlineStr">
         <is>
           <t>负数模版取反</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>行项目.含税金额</t>
         </is>
@@ -4654,19 +4696,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E53" s="75" t="inlineStr">
+      <c r="E53" s="84" t="inlineStr">
         <is>
           <t>金额 + 税额</t>
         </is>
       </c>
-      <c r="F53" s="75" t="inlineStr">
+      <c r="F53" s="84" t="inlineStr">
         <is>
           <t>CA/VC</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>行项目.含税金额.NEG</t>
         </is>
@@ -4676,19 +4718,19 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E54" s="75" t="inlineStr">
+      <c r="E54" s="84" t="inlineStr">
         <is>
           <t>(金额+税额) * (-1)</t>
         </is>
       </c>
-      <c r="F54" s="75" t="inlineStr">
+      <c r="F54" s="84" t="inlineStr">
         <is>
           <t>负数模版取反</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>GST(10%).AU</t>
         </is>
@@ -4698,30 +4740,30 @@
           <t>公式计算</t>
         </is>
       </c>
-      <c r="E55" s="75" t="inlineStr">
+      <c r="E55" s="84" t="inlineStr">
         <is>
           <t>金额 * 10%</t>
         </is>
       </c>
-      <c r="F55" s="75" t="inlineStr">
+      <c r="F55" s="84" t="inlineStr">
         <is>
           <t>澳洲</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="73" t="inlineStr">
+      <c r="B56" s="82" t="inlineStr">
         <is>
           <t>主体预设字段</t>
         </is>
       </c>
-      <c r="C56" s="74" t="n"/>
-      <c r="D56" s="74" t="n"/>
-      <c r="E56" s="74" t="n"/>
-      <c r="F56" s="74" t="n"/>
+      <c r="C56" s="83" t="n"/>
+      <c r="D56" s="83" t="n"/>
+      <c r="E56" s="83" t="n"/>
+      <c r="F56" s="83" t="n"/>
     </row>
     <row r="57">
-      <c r="C57" s="14" t="inlineStr">
+      <c r="C57" s="15" t="inlineStr">
         <is>
           <t>收款人名称</t>
         </is>
@@ -4731,19 +4773,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E57" s="75" t="inlineStr">
+      <c r="E57" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;收款人名称</t>
         </is>
       </c>
-      <c r="F57" s="75" t="inlineStr">
+      <c r="F57" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C58" s="15" t="inlineStr">
         <is>
           <t>银行名称</t>
         </is>
@@ -4753,19 +4795,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E58" s="75" t="inlineStr">
+      <c r="E58" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;银行名称</t>
         </is>
       </c>
-      <c r="F58" s="75" t="inlineStr">
+      <c r="F58" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="14" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>账户名称</t>
         </is>
@@ -4775,19 +4817,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E59" s="75" t="inlineStr">
+      <c r="E59" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;账户名称</t>
         </is>
       </c>
-      <c r="F59" s="75" t="inlineStr">
+      <c r="F59" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>账号</t>
         </is>
@@ -4797,19 +4839,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E60" s="75" t="inlineStr">
+      <c r="E60" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;账号</t>
         </is>
       </c>
-      <c r="F60" s="75" t="inlineStr">
+      <c r="F60" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="14" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>银行代码</t>
         </is>
@@ -4819,19 +4861,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E61" s="75" t="inlineStr">
+      <c r="E61" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;银行代码</t>
         </is>
       </c>
-      <c r="F61" s="75" t="inlineStr">
+      <c r="F61" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>Swift Code</t>
         </is>
@@ -4841,19 +4883,19 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E62" s="75" t="inlineStr">
+      <c r="E62" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;Swift Code</t>
         </is>
       </c>
-      <c r="F62" s="75" t="inlineStr">
+      <c r="F62" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="14" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>银行地址</t>
         </is>
@@ -4863,30 +4905,30 @@
           <t>字段映射</t>
         </is>
       </c>
-      <c r="E63" s="75" t="inlineStr">
+      <c r="E63" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;银行地址</t>
         </is>
       </c>
-      <c r="F63" s="75" t="inlineStr">
+      <c r="F63" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="73" t="inlineStr">
+      <c r="B64" s="82" t="inlineStr">
         <is>
           <t>开票主体/收款信息</t>
         </is>
       </c>
-      <c r="C64" s="74" t="n"/>
-      <c r="D64" s="74" t="n"/>
-      <c r="E64" s="74" t="n"/>
-      <c r="F64" s="74" t="n"/>
+      <c r="C64" s="83" t="n"/>
+      <c r="D64" s="83" t="n"/>
+      <c r="E64" s="83" t="n"/>
+      <c r="F64" s="83" t="n"/>
     </row>
     <row r="65">
-      <c r="C65" s="14" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>开票主体</t>
         </is>
@@ -4896,19 +4938,19 @@
           <t>主体预设</t>
         </is>
       </c>
-      <c r="E65" s="75" t="inlineStr">
+      <c r="E65" s="84" t="inlineStr">
         <is>
           <t>主体信息-&gt;名称</t>
         </is>
       </c>
-      <c r="F65" s="75" t="inlineStr">
+      <c r="F65" s="84" t="inlineStr">
         <is>
           <t>FBU</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>收款信息</t>
         </is>
@@ -4918,19 +4960,19 @@
           <t>主体预设</t>
         </is>
       </c>
-      <c r="E66" s="75" t="inlineStr">
+      <c r="E66" s="84" t="inlineStr">
         <is>
           <t>主体信息-&gt;收款银行信息</t>
         </is>
       </c>
-      <c r="F66" s="75" t="inlineStr">
+      <c r="F66" s="84" t="inlineStr">
         <is>
           <t>FBU</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="14" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t>销售方名称（中文）</t>
         </is>
@@ -4940,19 +4982,19 @@
           <t>主体预设</t>
         </is>
       </c>
-      <c r="E67" s="75" t="inlineStr">
+      <c r="E67" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;中文名称</t>
         </is>
       </c>
-      <c r="F67" s="75" t="inlineStr">
+      <c r="F67" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr">
         <is>
           <t>销售方名称（英文）</t>
         </is>
@@ -4962,19 +5004,19 @@
           <t>主体预设</t>
         </is>
       </c>
-      <c r="E68" s="75" t="inlineStr">
+      <c r="E68" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;英文名称</t>
         </is>
       </c>
-      <c r="F68" s="75" t="inlineStr">
+      <c r="F68" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="C69" s="14" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>销售方地址（中文）</t>
         </is>
@@ -4984,19 +5026,19 @@
           <t>主体预设</t>
         </is>
       </c>
-      <c r="E69" s="75" t="inlineStr">
+      <c r="E69" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;中文地址</t>
         </is>
       </c>
-      <c r="F69" s="75" t="inlineStr">
+      <c r="F69" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>销售方地址（英文）</t>
         </is>
@@ -5006,12 +5048,12 @@
           <t>主体预设</t>
         </is>
       </c>
-      <c r="E70" s="75" t="inlineStr">
+      <c r="E70" s="84" t="inlineStr">
         <is>
           <t>主体-&gt;英文地址</t>
         </is>
       </c>
-      <c r="F70" s="75" t="inlineStr">
+      <c r="F70" s="84" t="inlineStr">
         <is>
           <t>ABU</t>
         </is>
@@ -5112,21 +5154,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="55" t="inlineStr">
+      <c r="A1" s="85" t="inlineStr">
         <is>
           <t>发票模板导入规则说明</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="76" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>一、核心颜色规则</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="77" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>黑色字体</t>
         </is>
@@ -5138,7 +5180,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="77" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t>红色字体(RGB#FF0000)</t>
         </is>
@@ -5150,14 +5192,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="76" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>二、行项目区</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="87" t="inlineStr">
         <is>
           <t>行项目字段</t>
         </is>
@@ -5169,14 +5211,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="76" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>三、字段作用域</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="77" t="inlineStr">
+      <c r="A11" s="87" t="inlineStr">
         <is>
           <t>同名不同规</t>
         </is>
@@ -5188,7 +5230,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="87" t="inlineStr">
         <is>
           <t>共享复用</t>
         </is>
@@ -5200,14 +5242,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="76" t="inlineStr">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>四、正数/负数发票</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="87" t="inlineStr">
         <is>
           <t>双模板并存</t>
         </is>
@@ -5219,7 +5261,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="87" t="inlineStr">
         <is>
           <t>自动选择</t>
         </is>
@@ -5231,14 +5273,14 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="76" t="inlineStr">
+      <c r="A18" s="86" t="inlineStr">
         <is>
           <t>五、多税率模板</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="77" t="inlineStr">
+      <c r="A19" s="87" t="inlineStr">
         <is>
           <t>分税率模板</t>
         </is>
@@ -5250,7 +5292,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="77" t="inlineStr">
+      <c r="A20" s="87" t="inlineStr">
         <is>
           <t>自动匹配</t>
         </is>
@@ -5262,14 +5304,14 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="76" t="inlineStr">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>六、关键约束</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="87" t="inlineStr">
         <is>
           <t>银行区</t>
         </is>
@@ -5281,7 +5323,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="77" t="inlineStr">
+      <c r="A24" s="87" t="inlineStr">
         <is>
           <t>编码规则分离</t>
         </is>
@@ -5293,7 +5335,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="87" t="inlineStr">
         <is>
           <t>字段取值规则</t>
         </is>
@@ -5305,14 +5347,14 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="76" t="inlineStr">
+      <c r="A27" s="86" t="inlineStr">
         <is>
           <t>七、模版生命周期管理</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="77" t="inlineStr">
+      <c r="A28" s="87" t="inlineStr">
         <is>
           <t>模版编码</t>
         </is>
@@ -5324,7 +5366,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="77" t="inlineStr">
+      <c r="A29" s="87" t="inlineStr">
         <is>
           <t>三区自动划分</t>
         </is>
@@ -5336,7 +5378,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="77" t="inlineStr">
+      <c r="A30" s="87" t="inlineStr">
         <is>
           <t>新增导入</t>
         </is>
@@ -5348,7 +5390,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="77" t="inlineStr">
+      <c r="A31" s="87" t="inlineStr">
         <is>
           <t>更新导入</t>
         </is>
@@ -5360,7 +5402,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="87" t="inlineStr">
         <is>
           <t>禁用</t>
         </is>
@@ -5372,7 +5414,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="77" t="inlineStr">
+      <c r="A33" s="87" t="inlineStr">
         <is>
           <t>开票用最新版</t>
         </is>
@@ -5432,28 +5474,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
@@ -5478,113 +5520,113 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.CA</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>GST 5%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
@@ -5592,87 +5634,87 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>合计税额</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>合计含税金额</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: GOODCANG LOGISTICS CANADA CORP.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 5 Paget Road, Brampton, ON L6T 5S2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Bank name: Aberdeen Centre Branch</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank Address: 1160-4151 Hazelbridge Way, Richmond V6X 4J7</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Bank Transit: 03395</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Fiancial Institution: 003</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: ROYCCAT2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Account#: 033951001429(CAD)</t>
         </is>
@@ -5734,28 +5776,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
@@ -5780,113 +5822,113 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.CA</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>GST 5%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额.NEG</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
@@ -5894,87 +5936,87 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>合计税额.NEG</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>合计含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: GOODCANG LOGISTICS CANADA CORP.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 5 Paget Road, Brampton, ON L6T 5S2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Bank name: Aberdeen Centre Branch</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank Address: 1160-4151 Hazelbridge Way, Richmond V6X 4J7</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Bank Transit: 03395</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Fiancial Institution: 003</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: ROYCCAT2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Account#: 033951001429(CAD)</t>
         </is>
@@ -6036,28 +6078,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
@@ -6082,113 +6124,113 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.CA</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>HST 13%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
@@ -6196,87 +6238,87 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>合计税额</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>合计含税金额</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: GOODCANG LOGISTICS CANADA CORP.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 5 Paget Road, Brampton, ON L6T 5S2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Bank name: Aberdeen Centre Branch</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank Address: 1160-4151 Hazelbridge Way, Richmond V6X 4J7</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Bank Transit: 03395</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Fiancial Institution: 003</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: ROYCCAT2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Account#: 033951001429(CAD)</t>
         </is>
@@ -6338,28 +6380,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
@@ -6384,113 +6426,113 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.CA</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.US</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>HST 13%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额.NEG</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
@@ -6498,87 +6540,87 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="15" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>合计税额.NEG</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>合计含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: GOODCANG LOGISTICS CANADA CORP.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 5 Paget Road, Brampton, ON L6T 5S2</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Bank name: Aberdeen Centre Branch</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank Address: 1160-4151 Hazelbridge Way, Richmond V6X 4J7</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Bank Transit: 03395</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Fiancial Institution: 003</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: ROYCCAT2</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Account#: 033951001429(CAD)</t>
         </is>
@@ -6633,28 +6675,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
@@ -6679,132 +6721,132 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.VC</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.VC</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>CURRENCY: CANADIAN DOLLAR</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>GST 0%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
@@ -6812,62 +6854,62 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>合计税额</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>合计含税金额</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: Zenda Logistics Corp.</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 105-19159 22ND AVENUE SURREY BC V3Z 3S6 CANADA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank name: Scotiabank</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: NOSCCATT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Account#: 0114618</t>
         </is>
@@ -6921,28 +6963,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
@@ -6967,132 +7009,132 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.VC</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.VC</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>CURRENCY: CANADIAN DOLLAR</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>GST 0%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额.NEG</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
@@ -7100,62 +7142,62 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>合计税额.NEG</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>合计含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: Zenda Logistics Corp.</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 105-19159 22ND AVENUE SURREY BC V3Z 3S6 CANADA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank name: Scotiabank</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: NOSCCATT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Account#: 0114618</t>
         </is>
@@ -7209,28 +7251,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>INVOICE</t>
         </is>
@@ -7255,132 +7297,132 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.VC</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.VC</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>CURRENCY: CANADIAN DOLLAR</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>HST 13%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
@@ -7388,62 +7430,62 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>合计金额</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>合计税额</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>合计含税金额</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: Zenda Logistics Corp.</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 105-19159 22ND AVENUE SURREY BC V3Z 3S6 CANADA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank name: Scotiabank</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: NOSCCATT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Account#: 0114618</t>
         </is>
@@ -7497,28 +7539,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Bill to:</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>客户名称</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>客户地址</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Credit Note</t>
         </is>
@@ -7543,132 +7585,132 @@
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>发票号码.VC</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>开票日期.VC</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>付款周期</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>CURRENCY: CANADIAN DOLLAR</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>HST 13%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>行项目.描述.US</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>行项目.金额.NEG</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>行项目.税额.NEG</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>行项目.含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="5" t="inlineStr">
@@ -7676,62 +7718,62 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="15" t="inlineStr">
         <is>
           <t>合计金额.NEG</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>合计税额.NEG</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>合计含税金额.NEG</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>发票备注</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Please remit to :</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary: Zenda Logistics Corp.</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Beneficiary's address: 105-19159 22ND AVENUE SURREY BC V3Z 3S6 CANADA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Bank name: Scotiabank</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>SWIFT Code: NOSCCATT</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Account#: 0114618</t>
         </is>
